--- a/reviews/a-envoyer/otea-filmakers-2026-08-31.xlsx
+++ b/reviews/a-envoyer/otea-filmakers-2026-08-31.xlsx
@@ -896,7 +896,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28T06:09:04</t>
+          <t>2026-08-28T17:14:09</t>
         </is>
       </c>
     </row>
